--- a/data/trans_orig/P63-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P63-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112869</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87608</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204426</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96177</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138079</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269559</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>525395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>527263</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>404989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>406923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>932288</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934186</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161726</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163605</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>520090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1246824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1248760</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1545037</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1546960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1032200</t>
+          <t>1034208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1091864</t>
+          <t>1090905</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1053538</t>
+          <t>1052363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1148063</t>
+          <t>1149567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2105880</t>
+          <t>2101897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2223486</t>
+          <t>2219873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>269639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>328344</t>
+          <t>326336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1200871</t>
+          <t>1199367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1295396</t>
+          <t>1296571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1485992</t>
+          <t>1489605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1603598</t>
+          <t>1607581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161265</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167781</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169911</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>331176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>346719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>348825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>493228</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>724884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>462652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>464737</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1187550</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1189621</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>355712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>357708</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>583822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>585890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>941555</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>943598</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1107312</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1109351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1374215</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1376233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1698545</t>
+          <t>1695192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1756878</t>
+          <t>1755838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1433281</t>
+          <t>1434320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1535756</t>
+          <t>1535416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3150911</t>
+          <t>3149317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3270752</t>
+          <t>3280460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237095</t>
+          <t>238135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>295428</t>
+          <t>298781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1059647</t>
+          <t>1059987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1162122</t>
+          <t>1161083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318623</t>
+          <t>1308915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1438464</t>
+          <t>1440058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148731</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130826</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>281588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283634</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>314276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316293</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>302698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>401570</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403577</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>660913</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>457826</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1116742</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1118740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>424793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>426739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>538582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>540625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>965362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>967364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1079933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1082025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1367091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1369170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1641074</t>
+          <t>1645133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1706436</t>
+          <t>1706241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1361163</t>
+          <t>1361597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1460841</t>
+          <t>1461381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3025069</t>
+          <t>3021139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3154416</t>
+          <t>3149451</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256964</t>
+          <t>257159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>322326</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1034536</t>
+          <t>1033996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1134214</t>
+          <t>1133780</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1304361</t>
+          <t>1309326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1433708</t>
+          <t>1437638</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023 (tasa de respuesta: 98,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>151918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>282036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177189</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>472309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>549702</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1023678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>233272</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>464350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>465393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>699029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>760111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1000365</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1141169</t>
+          <t>1139457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1232963</t>
+          <t>1228964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1276711</t>
+          <t>1271681</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1577574</t>
+          <t>1579494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2466941</t>
+          <t>2470152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2755153</t>
+          <t>2753656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195932</t>
+          <t>199931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287726</t>
+          <t>289438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>553807</t>
+          <t>551887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>854670</t>
+          <t>859700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>805123</t>
+          <t>806620</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1093335</t>
+          <t>1090124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P63-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P63-Clase-trans_orig.xlsx
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1034208</t>
+          <t>1032443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1090905</t>
+          <t>1091882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1049832</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1149567</t>
+          <t>1146176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2101897</t>
+          <t>2106462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2219873</t>
+          <t>2223627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>269639</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>326336</t>
+          <t>328101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1199367</t>
+          <t>1202758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1296571</t>
+          <t>1299102</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1489605</t>
+          <t>1485851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1607581</t>
+          <t>1603016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1695192</t>
+          <t>1698246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1755838</t>
+          <t>1756512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1434320</t>
+          <t>1436040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1535416</t>
+          <t>1537839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3149317</t>
+          <t>3149311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3280460</t>
+          <t>3271409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238135</t>
+          <t>237461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>298781</t>
+          <t>295727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1059987</t>
+          <t>1057564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1161083</t>
+          <t>1159363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1308915</t>
+          <t>1317966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1440058</t>
+          <t>1440064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1645133</t>
+          <t>1642655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1706241</t>
+          <t>1706253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1361597</t>
+          <t>1363543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1461381</t>
+          <t>1461270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3021139</t>
+          <t>3028552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3149451</t>
+          <t>3158206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257159</t>
+          <t>257147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318267</t>
+          <t>320745</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033996</t>
+          <t>1034107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1133780</t>
+          <t>1131834</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1309326</t>
+          <t>1300571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1437638</t>
+          <t>1430225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>148719</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>148719</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>148719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>148719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>465393</t>
+          <t>516402</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>773833</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>465393</t>
+          <t>516402</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>465393</t>
+          <t>516402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>465393</t>
+          <t>516402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>773833</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>773833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>773833</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1188388</t>
+          <t>1295698</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1139457</t>
+          <t>1256518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1228964</t>
+          <t>1336405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1370010</t>
+          <t>1301073</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1271681</t>
+          <t>1257758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1579494</t>
+          <t>1343496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2558398</t>
+          <t>2596771</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2470152</t>
+          <t>2534636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2753656</t>
+          <t>2653794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199931</t>
+          <t>196521</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289438</t>
+          <t>276408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>551887</t>
+          <t>801858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>859700</t>
+          <t>887596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>806620</t>
+          <t>1024486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1090124</t>
+          <t>1143644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1428895</t>
+          <t>1532926</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1428895</t>
+          <t>1532926</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1428895</t>
+          <t>1532926</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2131381</t>
+          <t>2145354</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2131381</t>
+          <t>2145354</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2131381</t>
+          <t>2145354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3560276</t>
+          <t>3678280</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3560276</t>
+          <t>3678280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3560276</t>
+          <t>3678280</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
